--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30954-2026 artfynd.xlsx
+++ b/artfynd/A 30954-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136720408</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136720407</v>
       </c>
       <c r="B3" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136720409</v>
       </c>
       <c r="B4" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
